--- a/data/3.8.2/0. base-year_2015/extensions/dom_biogeochemical/d_cba.xlsx
+++ b/data/3.8.2/0. base-year_2015/extensions/dom_biogeochemical/d_cba.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ademecloud.sharepoint.com/sites/P-ConventionsSMASH-CIRED/Documents partages/General/Convention 5 - PlanéFR/shared_data/260227-outputs_MatMat/1-transitions_2050/3.8.2/base-year_2015/extensions/dom_biogeochemical/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\3.8.2\0. base-year_2015\extensions\dom_biogeochemical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_B5BBC12BCE7470465648CFDAEA0A668A7A95220A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1EA2F89-1A20-4247-98DD-0369DC0E1FA8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F63C8F-8038-4B84-B350-56A15FE3F357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1210,12 +1213,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:ATE16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2422,7 +2425,7 @@
       <c r="ATD1" s="2"/>
       <c r="ATE1" s="2"/>
     </row>
-    <row r="2" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3635,7 +3638,7 @@
       <c r="ATD2" s="2"/>
       <c r="ATE2" s="2"/>
     </row>
-    <row r="3" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -4852,7 +4855,7 @@
       <c r="ATD3" s="2"/>
       <c r="ATE3" s="2"/>
     </row>
-    <row r="4" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -6237,7 +6240,7 @@
       <c r="ATD4" s="2"/>
       <c r="ATE4" s="2"/>
     </row>
-    <row r="5" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -8282,7 +8285,7 @@
       <c r="ATD5" s="2"/>
       <c r="ATE5" s="2"/>
     </row>
-    <row r="6" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>58</v>
       </c>
@@ -11887,12 +11890,12 @@
         <v>258</v>
       </c>
     </row>
-    <row r="7" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="8" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>260</v>
       </c>
@@ -15497,7 +15500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>261</v>
       </c>
@@ -19102,7 +19105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>262</v>
       </c>
@@ -22707,7 +22710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>263</v>
       </c>
@@ -26312,7 +26315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>264</v>
       </c>
@@ -29917,7 +29920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>265</v>
       </c>
@@ -33522,7 +33525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>266</v>
       </c>
@@ -37127,7 +37130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>267</v>
       </c>
@@ -40732,7 +40735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:1201" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1201" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>268</v>
       </c>
@@ -44339,26 +44342,239 @@
     </row>
   </sheetData>
   <mergeCells count="281">
-    <mergeCell ref="ART5:ASC5"/>
-    <mergeCell ref="AEO4:AFK4"/>
-    <mergeCell ref="PE5:PP5"/>
-    <mergeCell ref="SF5:SG5"/>
-    <mergeCell ref="U4:AQ4"/>
-    <mergeCell ref="AFL5:AFW5"/>
-    <mergeCell ref="ALI5:ALM5"/>
-    <mergeCell ref="YO4:ZJ4"/>
-    <mergeCell ref="ACG5:ACH5"/>
-    <mergeCell ref="KK4:LP4"/>
-    <mergeCell ref="ABO5:ABR5"/>
-    <mergeCell ref="LL5:LM5"/>
-    <mergeCell ref="NM4:OF4"/>
-    <mergeCell ref="AGG4:AHB4"/>
-    <mergeCell ref="AR5:BC5"/>
-    <mergeCell ref="CV5:CW5"/>
-    <mergeCell ref="CS4:DX4"/>
-    <mergeCell ref="CP5:CR5"/>
-    <mergeCell ref="AG5:AN5"/>
-    <mergeCell ref="AEO5:AEZ5"/>
+    <mergeCell ref="DM5:DS5"/>
+    <mergeCell ref="ARJ5:ARL5"/>
+    <mergeCell ref="B1:ATE1"/>
+    <mergeCell ref="ARQ5:ARR5"/>
+    <mergeCell ref="MM5:MN5"/>
+    <mergeCell ref="AAV5:AAW5"/>
+    <mergeCell ref="ARN4:ARS4"/>
+    <mergeCell ref="KC5:KE5"/>
+    <mergeCell ref="ABM5:ABN5"/>
+    <mergeCell ref="ALN3:ATE3"/>
+    <mergeCell ref="QZ5:RE5"/>
+    <mergeCell ref="AHH4:AHL4"/>
+    <mergeCell ref="RF5:RG5"/>
+    <mergeCell ref="RI5:RQ5"/>
+    <mergeCell ref="CN4:CR4"/>
+    <mergeCell ref="JE4:JZ4"/>
+    <mergeCell ref="VS5:VX5"/>
+    <mergeCell ref="WL5:WT5"/>
+    <mergeCell ref="ALN5:ALU5"/>
+    <mergeCell ref="OL3:WC3"/>
+    <mergeCell ref="ASS5:AST5"/>
+    <mergeCell ref="ACT5:ACV5"/>
+    <mergeCell ref="U5:AF5"/>
+    <mergeCell ref="AND4:ANX4"/>
+    <mergeCell ref="CI4:CM4"/>
+    <mergeCell ref="CK5:CM5"/>
+    <mergeCell ref="AJY5:AJZ5"/>
+    <mergeCell ref="AHE5:AHG5"/>
+    <mergeCell ref="ASG4:ASZ4"/>
+    <mergeCell ref="LQ5:MB5"/>
+    <mergeCell ref="GO4:GS4"/>
+    <mergeCell ref="TW5:TZ5"/>
+    <mergeCell ref="B2:WC2"/>
+    <mergeCell ref="GT3:OK3"/>
+    <mergeCell ref="RX4:SB4"/>
+    <mergeCell ref="UR4:VD4"/>
+    <mergeCell ref="ALN4:AMF4"/>
+    <mergeCell ref="TU5:TV5"/>
+    <mergeCell ref="NM5:NS5"/>
+    <mergeCell ref="AMG4:ANC4"/>
+    <mergeCell ref="DV5:DX5"/>
+    <mergeCell ref="GT5:HA5"/>
+    <mergeCell ref="UE5:UF5"/>
+    <mergeCell ref="FH5:FQ5"/>
+    <mergeCell ref="AHJ5:AHL5"/>
+    <mergeCell ref="SC4:TH4"/>
+    <mergeCell ref="FB5:FD5"/>
+    <mergeCell ref="DT5:DU5"/>
+    <mergeCell ref="WD2:ADU2"/>
+    <mergeCell ref="ARG4:ARH4"/>
+    <mergeCell ref="JH5:JM5"/>
+    <mergeCell ref="ALI4:ALM4"/>
+    <mergeCell ref="AQW5:AQX5"/>
+    <mergeCell ref="B3:GS3"/>
+    <mergeCell ref="ART4:ASF4"/>
+    <mergeCell ref="AFL4:AGF4"/>
+    <mergeCell ref="ARG5:ARH5"/>
+    <mergeCell ref="FR5:FT5"/>
+    <mergeCell ref="BM4:CH4"/>
+    <mergeCell ref="AOW5:AOY5"/>
+    <mergeCell ref="ZR5:ZT5"/>
+    <mergeCell ref="AND5:ANO5"/>
+    <mergeCell ref="J5:R5"/>
+    <mergeCell ref="AHP5:AHQ5"/>
+    <mergeCell ref="PY5:QA5"/>
+    <mergeCell ref="UH5:UJ5"/>
+    <mergeCell ref="LQ4:MK4"/>
+    <mergeCell ref="AR4:BL4"/>
+    <mergeCell ref="NT5:NX5"/>
+    <mergeCell ref="ACD5:ACF5"/>
+    <mergeCell ref="ALA5:ALB5"/>
+    <mergeCell ref="AGG5:AGI5"/>
+    <mergeCell ref="WW5:XH5"/>
+    <mergeCell ref="DY5:EJ5"/>
+    <mergeCell ref="ME5:MH5"/>
+    <mergeCell ref="GT4:HL4"/>
+    <mergeCell ref="FH4:FT4"/>
+    <mergeCell ref="EU5:EV5"/>
+    <mergeCell ref="APY5:AQE5"/>
+    <mergeCell ref="APH5:API5"/>
+    <mergeCell ref="ANA5:ANC5"/>
+    <mergeCell ref="AOB5:AOG5"/>
+    <mergeCell ref="AJV4:AKA4"/>
+    <mergeCell ref="JN5:JO5"/>
+    <mergeCell ref="ZP4:ZT4"/>
+    <mergeCell ref="AIS4:AJM4"/>
+    <mergeCell ref="MZ4:NL4"/>
+    <mergeCell ref="ADQ4:ADU4"/>
+    <mergeCell ref="ADV5:AEC5"/>
+    <mergeCell ref="ADD5:ADH5"/>
+    <mergeCell ref="HY5:IF5"/>
+    <mergeCell ref="ALV5:AMD5"/>
+    <mergeCell ref="MM4:MN4"/>
+    <mergeCell ref="ANY5:AOA5"/>
+    <mergeCell ref="AMG5:AMR5"/>
+    <mergeCell ref="WW4:XS4"/>
+    <mergeCell ref="ADV4:AEN4"/>
+    <mergeCell ref="FU5:GA5"/>
+    <mergeCell ref="OL4:PD4"/>
+    <mergeCell ref="ABZ5:ACB5"/>
+    <mergeCell ref="VE5:VK5"/>
+    <mergeCell ref="APB5:APD5"/>
+    <mergeCell ref="OL5:OS5"/>
+    <mergeCell ref="ALN2:ATE2"/>
+    <mergeCell ref="ZM5:ZO5"/>
+    <mergeCell ref="AIS5:AJD5"/>
+    <mergeCell ref="AJE5:AJF5"/>
+    <mergeCell ref="VE4:VX4"/>
+    <mergeCell ref="ASG5:ASM5"/>
+    <mergeCell ref="AQH5:AQJ5"/>
+    <mergeCell ref="ACW4:ADP4"/>
+    <mergeCell ref="GG5:GH5"/>
+    <mergeCell ref="KN5:KO5"/>
+    <mergeCell ref="LN5:LP5"/>
+    <mergeCell ref="AHM4:AIR4"/>
+    <mergeCell ref="MZ5:NI5"/>
+    <mergeCell ref="AGP5:AGQ5"/>
+    <mergeCell ref="TF5:TH5"/>
+    <mergeCell ref="AKO4:ALH4"/>
+    <mergeCell ref="AHC4:AHG4"/>
+    <mergeCell ref="AFX5:AFZ5"/>
+    <mergeCell ref="ABY4:ACC4"/>
+    <mergeCell ref="AKB4:AKN4"/>
+    <mergeCell ref="JE5:JG5"/>
+    <mergeCell ref="AJO5:AJP5"/>
+    <mergeCell ref="AQF5:AQG5"/>
+    <mergeCell ref="ACW5:ADC5"/>
+    <mergeCell ref="GI5:GN5"/>
+    <mergeCell ref="AOU4:AOY4"/>
+    <mergeCell ref="RZ5:SB5"/>
+    <mergeCell ref="MC5:MD5"/>
+    <mergeCell ref="TI4:UC4"/>
+    <mergeCell ref="AIG5:AIM5"/>
+    <mergeCell ref="FU4:GN4"/>
+    <mergeCell ref="PE4:QA4"/>
+    <mergeCell ref="ZA5:ZI5"/>
+    <mergeCell ref="XQ5:XS5"/>
+    <mergeCell ref="B4:T4"/>
+    <mergeCell ref="ANY4:AOT4"/>
+    <mergeCell ref="APE4:AQJ4"/>
+    <mergeCell ref="RS4:RW4"/>
+    <mergeCell ref="BM5:BO5"/>
+    <mergeCell ref="VY5:WC5"/>
+    <mergeCell ref="SW5:TC5"/>
+    <mergeCell ref="ABW5:ABX5"/>
+    <mergeCell ref="ASD5:ASF5"/>
+    <mergeCell ref="ACD4:ACI4"/>
+    <mergeCell ref="ABA4:ABU4"/>
+    <mergeCell ref="ABW4:ABX4"/>
+    <mergeCell ref="UG4:UK4"/>
+    <mergeCell ref="VY4:WC4"/>
+    <mergeCell ref="AQK5:AQV5"/>
+    <mergeCell ref="IJ5:IU5"/>
+    <mergeCell ref="FE5:FF5"/>
+    <mergeCell ref="VB5:VD5"/>
+    <mergeCell ref="ZX5:ZY5"/>
+    <mergeCell ref="AJO4:AJP4"/>
+    <mergeCell ref="MP5:MR5"/>
+    <mergeCell ref="AGJ5:AGO5"/>
+    <mergeCell ref="EU4:EV4"/>
+    <mergeCell ref="AKO5:AKU5"/>
+    <mergeCell ref="ADV2:ALM2"/>
+    <mergeCell ref="HM4:II4"/>
+    <mergeCell ref="AO5:AQ5"/>
+    <mergeCell ref="ATA5:ATE5"/>
+    <mergeCell ref="OG5:OK5"/>
+    <mergeCell ref="AOH5:AOI5"/>
+    <mergeCell ref="RU5:RW5"/>
+    <mergeCell ref="UL5:UN5"/>
+    <mergeCell ref="ABA5:ABL5"/>
+    <mergeCell ref="ARI4:ARM4"/>
+    <mergeCell ref="TD5:TE5"/>
+    <mergeCell ref="AJG5:AJJ5"/>
+    <mergeCell ref="AFA5:AFH5"/>
+    <mergeCell ref="ACJ4:ACV4"/>
+    <mergeCell ref="ARN5:ARP5"/>
+    <mergeCell ref="AIP5:AIR5"/>
+    <mergeCell ref="WD4:WV4"/>
+    <mergeCell ref="IJ4:JD4"/>
+    <mergeCell ref="AKB5:AKK5"/>
+    <mergeCell ref="ADQ5:ADU5"/>
+    <mergeCell ref="XI5:XP5"/>
+    <mergeCell ref="JQ5:JY5"/>
+    <mergeCell ref="XT5:YE5"/>
+    <mergeCell ref="ALC5:ALH5"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="XT4:YN4"/>
+    <mergeCell ref="QB4:QV4"/>
+    <mergeCell ref="UO5:UP5"/>
+    <mergeCell ref="MW5:MX5"/>
+    <mergeCell ref="AMS5:AMZ5"/>
+    <mergeCell ref="AOK5:AOS5"/>
+    <mergeCell ref="MT4:MY4"/>
+    <mergeCell ref="AQK4:ARE4"/>
+    <mergeCell ref="EX5:EZ5"/>
+    <mergeCell ref="EK5:EL5"/>
+    <mergeCell ref="YR5:YW5"/>
+    <mergeCell ref="KF4:KJ4"/>
+    <mergeCell ref="QW4:RR4"/>
+    <mergeCell ref="AED5:AEL5"/>
+    <mergeCell ref="AFI5:AFK5"/>
+    <mergeCell ref="UL4:UQ4"/>
+    <mergeCell ref="AKV5:AKZ5"/>
+    <mergeCell ref="BP5:BU5"/>
+    <mergeCell ref="UE4:UF4"/>
+    <mergeCell ref="GB5:GF5"/>
+    <mergeCell ref="YO5:YQ5"/>
+    <mergeCell ref="NY5:NZ5"/>
+    <mergeCell ref="WD5:WK5"/>
+    <mergeCell ref="ADV3:ALM3"/>
+    <mergeCell ref="AJR5:AJT5"/>
+    <mergeCell ref="AOZ4:APD4"/>
+    <mergeCell ref="AJV5:AJX5"/>
+    <mergeCell ref="AIN5:AIO5"/>
+    <mergeCell ref="AAX5:AAZ5"/>
+    <mergeCell ref="QW5:QY5"/>
+    <mergeCell ref="ACJ5:ACS5"/>
+    <mergeCell ref="KH5:KJ5"/>
+    <mergeCell ref="AGS5:AHA5"/>
+    <mergeCell ref="ADK5:ADP5"/>
+    <mergeCell ref="PQ5:PX5"/>
+    <mergeCell ref="QB5:QM5"/>
+    <mergeCell ref="ZU4:AAZ4"/>
+    <mergeCell ref="ANP5:ANR5"/>
+    <mergeCell ref="MT5:MV5"/>
+    <mergeCell ref="AJQ4:AJU4"/>
+    <mergeCell ref="QN5:QP5"/>
+    <mergeCell ref="VQ5:VR5"/>
+    <mergeCell ref="AKL5:AKN5"/>
+    <mergeCell ref="TI5:TT5"/>
+    <mergeCell ref="OG4:OK4"/>
+    <mergeCell ref="WD3:ADU3"/>
+    <mergeCell ref="UR5:VA5"/>
     <mergeCell ref="ASU5:ASZ5"/>
     <mergeCell ref="KA4:KE4"/>
     <mergeCell ref="IV5:IX5"/>
@@ -44383,249 +44599,45 @@
     <mergeCell ref="AAO5:AAU5"/>
     <mergeCell ref="VL5:VP5"/>
     <mergeCell ref="ADI5:ADJ5"/>
-    <mergeCell ref="ADV3:ALM3"/>
-    <mergeCell ref="AJR5:AJT5"/>
-    <mergeCell ref="AOZ4:APD4"/>
-    <mergeCell ref="AJV5:AJX5"/>
-    <mergeCell ref="AIN5:AIO5"/>
-    <mergeCell ref="AAX5:AAZ5"/>
-    <mergeCell ref="QW5:QY5"/>
-    <mergeCell ref="ACJ5:ACS5"/>
-    <mergeCell ref="KH5:KJ5"/>
-    <mergeCell ref="AGS5:AHA5"/>
-    <mergeCell ref="ADK5:ADP5"/>
-    <mergeCell ref="PQ5:PX5"/>
-    <mergeCell ref="QB5:QM5"/>
-    <mergeCell ref="ZU4:AAZ4"/>
-    <mergeCell ref="ANP5:ANR5"/>
-    <mergeCell ref="MT5:MV5"/>
-    <mergeCell ref="AJQ4:AJU4"/>
-    <mergeCell ref="QN5:QP5"/>
-    <mergeCell ref="VQ5:VR5"/>
-    <mergeCell ref="AKL5:AKN5"/>
-    <mergeCell ref="TI5:TT5"/>
-    <mergeCell ref="OG4:OK4"/>
-    <mergeCell ref="WD3:ADU3"/>
-    <mergeCell ref="UR5:VA5"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="XT4:YN4"/>
-    <mergeCell ref="QB4:QV4"/>
-    <mergeCell ref="UO5:UP5"/>
-    <mergeCell ref="MW5:MX5"/>
-    <mergeCell ref="AMS5:AMZ5"/>
-    <mergeCell ref="AOK5:AOS5"/>
-    <mergeCell ref="MT4:MY4"/>
-    <mergeCell ref="AQK4:ARE4"/>
-    <mergeCell ref="EX5:EZ5"/>
-    <mergeCell ref="EK5:EL5"/>
-    <mergeCell ref="YR5:YW5"/>
-    <mergeCell ref="KF4:KJ4"/>
-    <mergeCell ref="QW4:RR4"/>
-    <mergeCell ref="AED5:AEL5"/>
-    <mergeCell ref="AFI5:AFK5"/>
-    <mergeCell ref="UL4:UQ4"/>
-    <mergeCell ref="AKV5:AKZ5"/>
-    <mergeCell ref="BP5:BU5"/>
-    <mergeCell ref="UE4:UF4"/>
-    <mergeCell ref="GB5:GF5"/>
-    <mergeCell ref="YO5:YQ5"/>
-    <mergeCell ref="NY5:NZ5"/>
-    <mergeCell ref="WD5:WK5"/>
-    <mergeCell ref="ADV2:ALM2"/>
-    <mergeCell ref="HM4:II4"/>
-    <mergeCell ref="AO5:AQ5"/>
-    <mergeCell ref="ATA5:ATE5"/>
-    <mergeCell ref="OG5:OK5"/>
-    <mergeCell ref="AOH5:AOI5"/>
-    <mergeCell ref="RU5:RW5"/>
-    <mergeCell ref="UL5:UN5"/>
-    <mergeCell ref="ABA5:ABL5"/>
-    <mergeCell ref="ARI4:ARM4"/>
-    <mergeCell ref="TD5:TE5"/>
-    <mergeCell ref="AJG5:AJJ5"/>
-    <mergeCell ref="AFA5:AFH5"/>
-    <mergeCell ref="ACJ4:ACV4"/>
-    <mergeCell ref="ARN5:ARP5"/>
-    <mergeCell ref="AIP5:AIR5"/>
-    <mergeCell ref="WD4:WV4"/>
-    <mergeCell ref="IJ4:JD4"/>
-    <mergeCell ref="AKB5:AKK5"/>
-    <mergeCell ref="ADQ5:ADU5"/>
-    <mergeCell ref="XI5:XP5"/>
-    <mergeCell ref="JQ5:JY5"/>
-    <mergeCell ref="XT5:YE5"/>
-    <mergeCell ref="ALC5:ALH5"/>
-    <mergeCell ref="B4:T4"/>
-    <mergeCell ref="ANY4:AOT4"/>
-    <mergeCell ref="APE4:AQJ4"/>
-    <mergeCell ref="RS4:RW4"/>
-    <mergeCell ref="BM5:BO5"/>
-    <mergeCell ref="VY5:WC5"/>
-    <mergeCell ref="SW5:TC5"/>
-    <mergeCell ref="ABW5:ABX5"/>
-    <mergeCell ref="ASD5:ASF5"/>
-    <mergeCell ref="ACD4:ACI4"/>
-    <mergeCell ref="ABA4:ABU4"/>
-    <mergeCell ref="ABW4:ABX4"/>
-    <mergeCell ref="UG4:UK4"/>
-    <mergeCell ref="VY4:WC4"/>
-    <mergeCell ref="AQK5:AQV5"/>
-    <mergeCell ref="IJ5:IU5"/>
-    <mergeCell ref="FE5:FF5"/>
-    <mergeCell ref="VB5:VD5"/>
-    <mergeCell ref="ZX5:ZY5"/>
-    <mergeCell ref="AJO4:AJP4"/>
-    <mergeCell ref="MP5:MR5"/>
-    <mergeCell ref="AGJ5:AGO5"/>
-    <mergeCell ref="EU4:EV4"/>
-    <mergeCell ref="AKO5:AKU5"/>
+    <mergeCell ref="ART5:ASC5"/>
+    <mergeCell ref="AEO4:AFK4"/>
+    <mergeCell ref="PE5:PP5"/>
+    <mergeCell ref="SF5:SG5"/>
+    <mergeCell ref="U4:AQ4"/>
+    <mergeCell ref="AFL5:AFW5"/>
+    <mergeCell ref="ALI5:ALM5"/>
+    <mergeCell ref="YO4:ZJ4"/>
+    <mergeCell ref="ACG5:ACH5"/>
+    <mergeCell ref="KK4:LP4"/>
+    <mergeCell ref="ABO5:ABR5"/>
+    <mergeCell ref="LL5:LM5"/>
+    <mergeCell ref="NM4:OF4"/>
+    <mergeCell ref="AGG4:AHB4"/>
+    <mergeCell ref="AR5:BC5"/>
+    <mergeCell ref="CV5:CW5"/>
+    <mergeCell ref="CS4:DX4"/>
+    <mergeCell ref="CP5:CR5"/>
+    <mergeCell ref="AG5:AN5"/>
+    <mergeCell ref="AEO5:AEZ5"/>
     <mergeCell ref="BD5:BF5"/>
     <mergeCell ref="HB5:HJ5"/>
     <mergeCell ref="BV5:BW5"/>
     <mergeCell ref="BY5:CG5"/>
-    <mergeCell ref="ABY4:ACC4"/>
-    <mergeCell ref="AKB4:AKN4"/>
-    <mergeCell ref="JE5:JG5"/>
-    <mergeCell ref="AJO5:AJP5"/>
-    <mergeCell ref="AQF5:AQG5"/>
-    <mergeCell ref="ACW5:ADC5"/>
-    <mergeCell ref="GI5:GN5"/>
-    <mergeCell ref="AOU4:AOY4"/>
-    <mergeCell ref="RZ5:SB5"/>
-    <mergeCell ref="MC5:MD5"/>
-    <mergeCell ref="TI4:UC4"/>
-    <mergeCell ref="FU5:GA5"/>
-    <mergeCell ref="OL4:PD4"/>
-    <mergeCell ref="ABZ5:ACB5"/>
-    <mergeCell ref="VE5:VK5"/>
-    <mergeCell ref="APB5:APD5"/>
-    <mergeCell ref="OL5:OS5"/>
-    <mergeCell ref="ALN2:ATE2"/>
-    <mergeCell ref="ZM5:ZO5"/>
-    <mergeCell ref="AIS5:AJD5"/>
-    <mergeCell ref="AJE5:AJF5"/>
-    <mergeCell ref="VE4:VX4"/>
-    <mergeCell ref="DY5:EJ5"/>
-    <mergeCell ref="ME5:MH5"/>
-    <mergeCell ref="GT4:HL4"/>
-    <mergeCell ref="FH4:FT4"/>
-    <mergeCell ref="EU5:EV5"/>
-    <mergeCell ref="APY5:AQE5"/>
-    <mergeCell ref="APH5:API5"/>
-    <mergeCell ref="ANA5:ANC5"/>
-    <mergeCell ref="AOB5:AOG5"/>
-    <mergeCell ref="AJV4:AKA4"/>
-    <mergeCell ref="JN5:JO5"/>
-    <mergeCell ref="ZP4:ZT4"/>
-    <mergeCell ref="AIS4:AJM4"/>
-    <mergeCell ref="MZ4:NL4"/>
-    <mergeCell ref="ADQ4:ADU4"/>
-    <mergeCell ref="ADV5:AEC5"/>
-    <mergeCell ref="ADD5:ADH5"/>
-    <mergeCell ref="HY5:IF5"/>
-    <mergeCell ref="ALV5:AMD5"/>
-    <mergeCell ref="ASG5:ASM5"/>
-    <mergeCell ref="MM4:MN4"/>
-    <mergeCell ref="ANY5:AOA5"/>
-    <mergeCell ref="AMG5:AMR5"/>
-    <mergeCell ref="AQH5:AQJ5"/>
-    <mergeCell ref="WW4:XS4"/>
-    <mergeCell ref="ADV4:AEN4"/>
-    <mergeCell ref="ACW4:ADP4"/>
-    <mergeCell ref="GG5:GH5"/>
-    <mergeCell ref="KN5:KO5"/>
-    <mergeCell ref="LN5:LP5"/>
-    <mergeCell ref="AHM4:AIR4"/>
-    <mergeCell ref="MZ5:NI5"/>
-    <mergeCell ref="AGP5:AGQ5"/>
-    <mergeCell ref="TF5:TH5"/>
-    <mergeCell ref="AKO4:ALH4"/>
-    <mergeCell ref="AHC4:AHG4"/>
-    <mergeCell ref="AFX5:AFZ5"/>
-    <mergeCell ref="AIG5:AIM5"/>
-    <mergeCell ref="FU4:GN4"/>
-    <mergeCell ref="PE4:QA4"/>
-    <mergeCell ref="ZA5:ZI5"/>
-    <mergeCell ref="ARG4:ARH4"/>
-    <mergeCell ref="JH5:JM5"/>
-    <mergeCell ref="ALI4:ALM4"/>
-    <mergeCell ref="AQW5:AQX5"/>
-    <mergeCell ref="B3:GS3"/>
-    <mergeCell ref="ART4:ASF4"/>
-    <mergeCell ref="AFL4:AGF4"/>
-    <mergeCell ref="ARG5:ARH5"/>
-    <mergeCell ref="FR5:FT5"/>
-    <mergeCell ref="BM4:CH4"/>
-    <mergeCell ref="AOW5:AOY5"/>
-    <mergeCell ref="ZR5:ZT5"/>
-    <mergeCell ref="AND5:ANO5"/>
-    <mergeCell ref="J5:R5"/>
-    <mergeCell ref="AHP5:AHQ5"/>
-    <mergeCell ref="PY5:QA5"/>
-    <mergeCell ref="UH5:UJ5"/>
-    <mergeCell ref="LQ4:MK4"/>
-    <mergeCell ref="AR4:BL4"/>
-    <mergeCell ref="NT5:NX5"/>
-    <mergeCell ref="ACD5:ACF5"/>
-    <mergeCell ref="ALA5:ALB5"/>
-    <mergeCell ref="AGG5:AGI5"/>
-    <mergeCell ref="WW5:XH5"/>
-    <mergeCell ref="XQ5:XS5"/>
-    <mergeCell ref="CK5:CM5"/>
-    <mergeCell ref="AJY5:AJZ5"/>
-    <mergeCell ref="AHE5:AHG5"/>
-    <mergeCell ref="ASG4:ASZ4"/>
-    <mergeCell ref="LQ5:MB5"/>
-    <mergeCell ref="GO4:GS4"/>
-    <mergeCell ref="TW5:TZ5"/>
-    <mergeCell ref="B2:WC2"/>
-    <mergeCell ref="GT3:OK3"/>
-    <mergeCell ref="RX4:SB4"/>
-    <mergeCell ref="UR4:VD4"/>
-    <mergeCell ref="ALN4:AMF4"/>
-    <mergeCell ref="TU5:TV5"/>
-    <mergeCell ref="NM5:NS5"/>
-    <mergeCell ref="AMG4:ANC4"/>
-    <mergeCell ref="DV5:DX5"/>
-    <mergeCell ref="GT5:HA5"/>
-    <mergeCell ref="UE5:UF5"/>
-    <mergeCell ref="FH5:FQ5"/>
-    <mergeCell ref="AHJ5:AHL5"/>
-    <mergeCell ref="SC4:TH4"/>
-    <mergeCell ref="FB5:FD5"/>
-    <mergeCell ref="DT5:DU5"/>
-    <mergeCell ref="WD2:ADU2"/>
-    <mergeCell ref="ARJ5:ARL5"/>
-    <mergeCell ref="B1:ATE1"/>
-    <mergeCell ref="ARQ5:ARR5"/>
-    <mergeCell ref="MM5:MN5"/>
-    <mergeCell ref="AAV5:AAW5"/>
-    <mergeCell ref="ARN4:ARS4"/>
-    <mergeCell ref="KC5:KE5"/>
-    <mergeCell ref="ABM5:ABN5"/>
-    <mergeCell ref="ALN3:ATE3"/>
-    <mergeCell ref="QZ5:RE5"/>
-    <mergeCell ref="AHH4:AHL4"/>
-    <mergeCell ref="RF5:RG5"/>
-    <mergeCell ref="RI5:RQ5"/>
-    <mergeCell ref="CN4:CR4"/>
-    <mergeCell ref="JE4:JZ4"/>
-    <mergeCell ref="VS5:VX5"/>
-    <mergeCell ref="WL5:WT5"/>
-    <mergeCell ref="ALN5:ALU5"/>
-    <mergeCell ref="OL3:WC3"/>
-    <mergeCell ref="ASS5:AST5"/>
-    <mergeCell ref="ACT5:ACV5"/>
-    <mergeCell ref="U5:AF5"/>
-    <mergeCell ref="AND4:ANX4"/>
-    <mergeCell ref="CI4:CM4"/>
-    <mergeCell ref="DM5:DS5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CDDBE4AC5AD34144A319C175B124CDA5" ma:contentTypeVersion="7" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="fc6499810b9fd453994c0b215026778e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="df3242dc-6eaf-41b4-ba9f-f9ed2a2fc658" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f2a1cb09faa248fb1b7a5ebc9a370fc2" ns2:_="">
     <xsd:import namespace="df3242dc-6eaf-41b4-ba9f-f9ed2a2fc658"/>
@@ -44787,15 +44799,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -44803,13 +44806,27 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB9A4D3-E9E9-4212-ABFA-1199EC81F88E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE6E4D0F-34D0-493B-B404-D7EF0CA81998}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE6E4D0F-34D0-493B-B404-D7EF0CA81998}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB9A4D3-E9E9-4212-ABFA-1199EC81F88E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="df3242dc-6eaf-41b4-ba9f-f9ed2a2fc658"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
